--- a/ZAC_zzx/results/three_way/三方对比.xlsx
+++ b/ZAC_zzx/results/three_way/三方对比.xlsx
@@ -455,7 +455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>判分口径：三法同架构（ZAC repro）、同判分器（ZAC simulator 五项模型）；qmap 列为 ICCAD'25 路由感知编译（astar 优先，失败回落 agnostic，配置见末列），其调度按 compare_zac 同款顺序时间戳约定计价（job=2×15+√(d/0.00275)，1q 指令 52μs，rydberg 0.36μs），测量/栅栏操作不入编译；时长为顺序保守上界，zzx/ZAC 为真实判分时长。</t>
+          <t>判分口径：三法同架构（ZAC repro）、同判分器（ZAC simulator 五项模型）；qmap 列为 ICCAD'25 路由感知编译（astar 优先，失败回落 agnostic，配置见末列），其调度按 compare_zac 同款顺序时间戳约定计价（job=2×15+√(d/0.00275)，1q 指令 52μs，rydberg 0.36μs），测量/栅栏操作不入编译；时长为顺序保守上界，zzx/ZAC 为真实判分时长。批次口径：ZAC/zzx 的 mv=rearrangeJob 摆渡班次数（班内多原子并行、互相过compatible_2d 四规则），qmap 的 mv=load…store 搬运作业数（阵列重排式，作业少而载客多）——mv 跨系统只作趋势参考；人次=原子乘车总次数（直接对应保真度项 0.999^(2×人次)），三方可比；轮数=门批(rydberg/@+cz)条数。</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>判分口径：三法同架构（ZAC repro）、同判分器（ZAC simulator 五项模型）；qmap 列为 ICCAD'25 路由感知编译（astar 优先，失败回落 agnostic，配置见末列），其调度按 compare_zac 同款顺序时间戳约定计价（job=2×15+√(d/0.00275)，1q 指令 52μs，rydberg 0.36μs），测量/栅栏操作不入编译；时长为顺序保守上界，zzx/ZAC 为真实判分时长。</t>
+          <t>判分口径：三法同架构（ZAC repro）、同判分器（ZAC simulator 五项模型）；qmap 列为 ICCAD'25 路由感知编译（astar 优先，失败回落 agnostic，配置见末列），其调度按 compare_zac 同款顺序时间戳约定计价（job=2×15+√(d/0.00275)，1q 指令 52μs，rydberg 0.36μs），测量/栅栏操作不入编译；时长为顺序保守上界，zzx/ZAC 为真实判分时长。批次口径：ZAC/zzx 的 mv=rearrangeJob 摆渡班次数（班内多原子并行、互相过compatible_2d 四规则），qmap 的 mv=load…store 搬运作业数（阵列重排式，作业少而载客多）——mv 跨系统只作趋势参考；人次=原子乘车总次数（直接对应保真度项 0.999^(2×人次)），三方可比；轮数=门批(rydberg/@+cz)条数。</t>
         </is>
       </c>
     </row>
